--- a/files/港岛-西营盘及上环-尚逸.xlsx
+++ b/files/港岛-西营盘及上环-尚逸.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="尚逸 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="尚逸" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -145,8 +171,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -193,19 +219,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,10 +237,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +645,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -8096,139 +8134,139 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>尚逸 - 尚逸 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>尚逸 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>161 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>160 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 641呎 (3房)
 招标单位
@@ -8236,18 +8274,18 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>B | 666呎 (3房)
-$2,800万
+$2800万
 $42,042/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr"/>
-      <c r="E6" s="18" t="inlineStr"/>
-      <c r="F6" s="18" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $850万
@@ -8255,7 +8293,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $830万
@@ -8264,21 +8302,21 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>A | 492呎 (3房)
-$1,499万
+$1499万
 $30,464/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 344呎 (1房)
 $982万
@@ -8286,17 +8324,17 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>C | 474呎 (3房)
-$1,397万
+$1397万
 $29,477/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="18" t="inlineStr"/>
-      <c r="F7" s="18" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr"/>
+      <c r="F6" s="22" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $749万
@@ -8304,7 +8342,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $723万
@@ -8313,21 +8351,21 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 492呎 (3房)
-$1,386万
+$1386万
 $28,167/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 344呎 (1房)
 $900万
@@ -8335,17 +8373,17 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 474呎 (3房)
-$1,294万
+$1294万
 $27,293/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr"/>
-      <c r="F8" s="18" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $736万
@@ -8353,7 +8391,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $691万
@@ -8362,21 +8400,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>A | 492呎 (3房)
-$1,304万
+$1304万
 $26,502/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>B | 344呎 (1房)
 $896万
@@ -8384,17 +8422,17 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>C | 474呎 (3房)
-$1,266万
+$1266万
 $26,711/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="18" t="inlineStr"/>
-      <c r="F9" s="18" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr"/>
+      <c r="F8" s="22" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $705万
@@ -8402,7 +8440,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $733万
@@ -8411,21 +8449,21 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>A | 492呎 (3房)
-$1,259万
+$1259万
 $25,583/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>B | 344呎 (1房)
 $883万
@@ -8433,17 +8471,17 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>C | 474呎 (3房)
-$1,194万
+$1194万
 $25,187/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr"/>
-      <c r="F10" s="18" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr"/>
+      <c r="F9" s="22" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $695万
@@ -8451,7 +8489,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $663万
@@ -8460,13 +8498,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $973万
@@ -8474,7 +8512,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $660万
@@ -8482,7 +8520,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $537万
@@ -8490,7 +8528,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $729万
@@ -8498,7 +8536,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $486万
@@ -8506,7 +8544,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="17" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $656万
@@ -8514,7 +8552,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $620万
@@ -8523,21 +8561,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
-$1,101万
+$1101万
 $28,296/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $650万
@@ -8545,7 +8583,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $525万
@@ -8553,7 +8591,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $711万
@@ -8561,7 +8599,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $481万
@@ -8569,7 +8607,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $646万
@@ -8577,7 +8615,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $618万
@@ -8586,13 +8624,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $989万
@@ -8600,7 +8638,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $691万
@@ -8608,7 +8646,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $520万
@@ -8616,7 +8654,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $686万
@@ -8624,7 +8662,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $476万
@@ -8632,7 +8670,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="17" t="inlineStr">
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $630万
@@ -8640,7 +8678,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $601万
@@ -8649,13 +8687,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $900万
@@ -8663,7 +8701,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $625万
@@ -8671,7 +8709,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $507万
@@ -8679,7 +8717,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $708万
@@ -8687,7 +8725,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $466万
@@ -8695,7 +8733,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $620万
@@ -8703,7 +8741,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $600万
@@ -8712,13 +8750,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $883万
@@ -8726,7 +8764,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $670万
@@ -8734,7 +8772,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $498万
@@ -8742,7 +8780,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $621万
@@ -8750,7 +8788,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $466万
@@ -8758,7 +8796,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="17" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $607万
@@ -8766,7 +8804,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $597万
@@ -8775,13 +8813,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $870万
@@ -8789,7 +8827,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $620万
@@ -8797,7 +8835,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $495万
@@ -8805,7 +8843,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $590万
@@ -8813,7 +8851,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $455万
@@ -8821,7 +8859,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="17" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $598万
@@ -8829,7 +8867,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $581万
@@ -8838,13 +8876,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $857万
@@ -8852,7 +8890,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $574万
@@ -8860,7 +8898,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $500万
@@ -8868,7 +8906,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $602万
@@ -8876,7 +8914,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $445万
@@ -8884,7 +8922,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="17" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $576万
@@ -8892,7 +8930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $575万
@@ -8901,13 +8939,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $845万
@@ -8915,7 +8953,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $566万
@@ -8923,7 +8961,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $528万
@@ -8931,7 +8969,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $623万
@@ -8939,7 +8977,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $448万
@@ -8947,7 +8985,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="17" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $614万
@@ -8955,7 +8993,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $569万
@@ -8964,13 +9002,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $832万
@@ -8978,7 +9016,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $554万
@@ -8986,7 +9024,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $523万
@@ -8994,7 +9032,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $572万
@@ -9002,7 +9040,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $436万
@@ -9010,7 +9048,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="17" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $564万
@@ -9018,7 +9056,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $607万
@@ -9027,13 +9065,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $820万
@@ -9041,7 +9079,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $548万
@@ -9049,7 +9087,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="17" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $481万
@@ -9057,7 +9095,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $610万
@@ -9065,7 +9103,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="17" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $438万
@@ -9073,7 +9111,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="17" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $558万
@@ -9081,7 +9119,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $601万
@@ -9090,13 +9128,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $870万
@@ -9104,7 +9142,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $543万
@@ -9112,7 +9150,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $478万
@@ -9120,7 +9158,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="17" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $560万
@@ -9128,7 +9166,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="17" t="inlineStr">
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $439万
@@ -9136,7 +9174,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="17" t="inlineStr">
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $552万
@@ -9144,7 +9182,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="17" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $555万
@@ -9153,13 +9191,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $796万
@@ -9167,7 +9205,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $532万
@@ -9175,7 +9213,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="17" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $459万
@@ -9183,7 +9221,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $548万
@@ -9191,7 +9229,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="17" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $425万
@@ -9199,7 +9237,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="17" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $541万
@@ -9207,7 +9245,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="17" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $544万
@@ -9216,13 +9254,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $790万
@@ -9230,7 +9268,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $572万
@@ -9238,7 +9276,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="17" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $438万
@@ -9246,7 +9284,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="17" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $543万
@@ -9254,7 +9292,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="17" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $426万
@@ -9262,7 +9300,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $540万
@@ -9270,7 +9308,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="17" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $577万
@@ -9279,13 +9317,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $824万
@@ -9293,7 +9331,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $525万
@@ -9301,7 +9339,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="17" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $426万
@@ -9309,7 +9347,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $545万
@@ -9317,7 +9355,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="17" t="inlineStr">
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $444万
@@ -9325,7 +9363,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="17" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $536万
@@ -9333,7 +9371,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="17" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $573万
@@ -9342,13 +9380,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $809万
@@ -9356,7 +9394,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $521万
@@ -9364,7 +9402,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="17" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $423万
@@ -9372,7 +9410,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="17" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $538万
@@ -9380,7 +9418,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="17" t="inlineStr">
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $415万
@@ -9388,7 +9426,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $531万
@@ -9396,7 +9434,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="17" t="inlineStr">
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $537万
@@ -9405,13 +9443,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $786万
@@ -9419,7 +9457,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $517万
@@ -9427,7 +9465,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="17" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $419万
@@ -9435,7 +9473,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="17" t="inlineStr">
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $530万
@@ -9443,7 +9481,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="17" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $405万
@@ -9451,7 +9489,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="17" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $515万
@@ -9459,7 +9497,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="17" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $524万
@@ -9468,13 +9506,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $764万
@@ -9482,7 +9520,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $543万
@@ -9490,7 +9528,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="17" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $418万
@@ -9498,7 +9536,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="17" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $518万
@@ -9506,7 +9544,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="17" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $401万
@@ -9514,7 +9552,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="17" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $509万
@@ -9522,7 +9560,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="17" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $513万
@@ -9531,13 +9569,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $749万
@@ -9545,7 +9583,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $538万
@@ -9553,7 +9591,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="17" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $450万
@@ -9561,7 +9599,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="17" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $553万
@@ -9569,7 +9607,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="17" t="inlineStr">
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $422万
@@ -9577,7 +9615,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="17" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 278呎 (1房)
 $508万
@@ -9585,7 +9623,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="17" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 275呎 (1房)
 $504万
@@ -9594,13 +9632,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 389呎 (2房)
 $720万
@@ -9608,7 +9646,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 268呎 (1房)
 $486万
@@ -9616,7 +9654,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="17" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 215呎 (开放式)
 $403万
@@ -9624,7 +9662,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 286呎 (1房)
 $494万
@@ -9632,7 +9670,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="17" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 213呎 (开放式)
 $411万
@@ -9640,8 +9678,8 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr"/>
-      <c r="H29" s="17" t="inlineStr">
+      <c r="G28" s="22" t="inlineStr"/>
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 277呎 (1房)
 $497万
@@ -9650,13 +9688,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>A | 351呎 (2房)
 $869万
@@ -9664,7 +9702,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>B | 231呎 (1房)
 $515万
@@ -9672,7 +9710,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="17" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 177呎 (开放式)
 $400万
@@ -9680,7 +9718,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 254呎 (1房)
 $533万
@@ -9688,9 +9726,9 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr"/>
-      <c r="G30" s="18" t="inlineStr"/>
-      <c r="H30" s="17" t="inlineStr">
+      <c r="F29" s="22" t="inlineStr"/>
+      <c r="G29" s="22" t="inlineStr"/>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 236呎 (1房)
 $534万
@@ -9701,7 +9739,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
